--- a/public/exports/29189439.xlsx
+++ b/public/exports/29189439.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports/29189439.xlsx
+++ b/public/exports/29189439.xlsx
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortdalvej 148</t>
+          <t xml:space="preserve">Klim Strandvej 11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387991</t>
+          <t xml:space="preserve">3388939</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>1013</v>
+        <v>1989</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045365</t>
+          <t xml:space="preserve">200045366</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klim Strandvej 11</t>
+          <t xml:space="preserve">Peter Løthsvej 3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3388939</t>
+          <t xml:space="preserve">3257747</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,16 +4560,16 @@
         </is>
       </c>
       <c r="J61">
-        <v>1989</v>
+        <v>2892</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045366</t>
+          <t xml:space="preserve">200045370</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Løthsvej 3</t>
+          <t xml:space="preserve">Borups Alle 8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257747</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>2892</v>
+        <v>5609</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045370</t>
+          <t xml:space="preserve">200045631</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-08</t>
+          <t xml:space="preserve">2021-02-15</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borups Alle 8</t>
+          <t xml:space="preserve">Aggersundvej 31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">389895</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>5609</v>
+        <v>4258</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045631</t>
+          <t xml:space="preserve">200046144</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-15</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4781,15 +4781,15 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J64">
-        <v>4258</v>
+        <v>2413</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046144</t>
+          <t xml:space="preserve">200046145</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggersundvej 31</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">389895</t>
+          <t xml:space="preserve">3245971</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J65">
-        <v>2413</v>
+        <v>2037</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046145</t>
+          <t xml:space="preserve">200047894</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-04-11</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Aggersundvej 3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3245971</t>
+          <t xml:space="preserve">389900, 389901</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>2037</v>
+        <v>5756</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047894</t>
+          <t xml:space="preserve">200047945</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-11</t>
+          <t xml:space="preserve">2021-04-12</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggersundvej 3</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">389900, 389901</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="J67">
-        <v>5756</v>
+        <v>1800</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047945</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-12</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J68">
-        <v>1800</v>
+        <v>1220</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5156,11 +5156,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J69">
-        <v>1220</v>
+        <v>679</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5231,11 +5231,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J70">
-        <v>679</v>
+        <v>4300</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5306,11 +5306,11 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J71">
-        <v>4300</v>
+        <v>2004</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5366,40 +5366,40 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J72">
-        <v>2004</v>
+        <v>449</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139958</t>
+          <t xml:space="preserve">311141837</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-13</t>
+          <t xml:space="preserve">2025-10-26</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,40 +5441,40 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Assenbækvej 2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9700</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">3240143</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>449</v>
+        <v>772</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141837</t>
+          <t xml:space="preserve">311146695</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-26</t>
+          <t xml:space="preserve">2025-11-23</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,17 +5516,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assenbækvej 2</t>
+          <t xml:space="preserve">Blokhusvej 41</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240143</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,11 +5535,11 @@
         </is>
       </c>
       <c r="J74">
-        <v>772</v>
+        <v>4595</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311146695</t>
+          <t xml:space="preserve">311147290</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-23</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 41</t>
+          <t xml:space="preserve">Blokhusvej 43</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J75">
-        <v>4595</v>
+        <v>1014</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 43</t>
+          <t xml:space="preserve">Bredgade 101</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,25 +5676,25 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3231646</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>1014</v>
+        <v>4245</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147290</t>
+          <t xml:space="preserve">311147235</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 101</t>
+          <t xml:space="preserve">Gerdsvej 1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9700</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231646</t>
+          <t xml:space="preserve">3239962</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,16 +5760,16 @@
         </is>
       </c>
       <c r="J77">
-        <v>4245</v>
+        <v>2045</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147235</t>
+          <t xml:space="preserve">311147288</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerdsvej 1</t>
+          <t xml:space="preserve">Lundbakvej 5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239962</t>
+          <t xml:space="preserve">3233529</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,16 +5835,16 @@
         </is>
       </c>
       <c r="J78">
-        <v>2045</v>
+        <v>3825</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147288</t>
+          <t xml:space="preserve">311147224</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbakvej 5</t>
+          <t xml:space="preserve">Nolsvej 1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233529</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,11 +5910,11 @@
         </is>
       </c>
       <c r="J79">
-        <v>3825</v>
+        <v>999</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147224</t>
+          <t xml:space="preserve">311147356</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1</t>
+          <t xml:space="preserve">Nolsvej 1A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5981,15 +5981,15 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J80">
-        <v>999</v>
+        <v>1405</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147356</t>
+          <t xml:space="preserve">311147369</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1A</t>
+          <t xml:space="preserve">Nolsvej 3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6056,15 +6056,15 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J81">
-        <v>1405</v>
+        <v>488</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147369</t>
+          <t xml:space="preserve">311147367</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6116,30 +6116,30 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 3</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J82">
-        <v>488</v>
+        <v>283</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147367</t>
+          <t xml:space="preserve">311147211</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Skolegade 4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6206,15 +6206,15 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J83">
-        <v>283</v>
+        <v>5012</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147211</t>
+          <t xml:space="preserve">311147212</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6281,11 +6281,11 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J84">
-        <v>5012</v>
+        <v>1840</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 4</t>
+          <t xml:space="preserve">Gammelgaardsvej 44</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,20 +6351,20 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">409816, 409817</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>1840</v>
+        <v>2162</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147212</t>
+          <t xml:space="preserve">311148091</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2025-12-01</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgaardsvej 44</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">409816, 409817</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6435,11 +6435,11 @@
         </is>
       </c>
       <c r="J86">
-        <v>2162</v>
+        <v>530</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148091</t>
+          <t xml:space="preserve">311149340</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-01</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J87">
-        <v>530</v>
+        <v>1424</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6566,30 +6566,30 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Præstegaardsvej 26A</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">3227505</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J88">
-        <v>1424</v>
+        <v>995</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149340</t>
+          <t xml:space="preserve">311161159</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2026-02-26</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,30 +6641,30 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 26A</t>
+          <t xml:space="preserve">Thomasmindeparken 1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227505</t>
+          <t xml:space="preserve">8369908</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>995</v>
+        <v>383</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311161159</t>
+          <t xml:space="preserve">311163902</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-26</t>
+          <t xml:space="preserve">2026-03-11</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomasmindeparken 1</t>
+          <t xml:space="preserve">Sundbyvej 30</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369908</t>
+          <t xml:space="preserve">3262677</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6735,11 +6735,11 @@
         </is>
       </c>
       <c r="J90">
-        <v>383</v>
+        <v>799</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311163902</t>
+          <t xml:space="preserve">311166177</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-11</t>
+          <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundbyvej 30</t>
+          <t xml:space="preserve">Lundbakvej 1D</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262677</t>
+          <t xml:space="preserve">3233518</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="J91">
-        <v>799</v>
+        <v>434</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166177</t>
+          <t xml:space="preserve">311168491</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-21</t>
+          <t xml:space="preserve">2026-04-05</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbakvej 1D</t>
+          <t xml:space="preserve">Hjorthsvej 7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233518</t>
+          <t xml:space="preserve">3239175</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="J92">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168491</t>
+          <t xml:space="preserve">311169236</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-05</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjorthsvej 7</t>
+          <t xml:space="preserve">Peter Løthsvej 10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239175</t>
+          <t xml:space="preserve">7752709</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="J93">
-        <v>487</v>
+        <v>912</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169236</t>
+          <t xml:space="preserve">311171770</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2026-04-20</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Løthsvej 10</t>
+          <t xml:space="preserve">Aaby Sdr. Gade 35</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752709</t>
+          <t xml:space="preserve">9134559</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="J94">
-        <v>912</v>
+        <v>5565</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311171770</t>
+          <t xml:space="preserve">311172317</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-20</t>
+          <t xml:space="preserve">2026-04-24</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaby Sdr. Gade 35</t>
+          <t xml:space="preserve">Kattedamsvej 26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9134559</t>
+          <t xml:space="preserve">3258634</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,11 +7110,11 @@
         </is>
       </c>
       <c r="J95">
-        <v>5565</v>
+        <v>8065</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311172317</t>
+          <t xml:space="preserve">311178208</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-24</t>
+          <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattedamsvej 26</t>
+          <t xml:space="preserve">Kattedamsvej 34</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7181,11 +7181,11 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J96">
-        <v>8065</v>
+        <v>289</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7241,40 +7241,40 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattedamsvej 34</t>
+          <t xml:space="preserve">Gustav Zimmersvej 29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258634</t>
+          <t xml:space="preserve">1413132</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>289</v>
+        <v>1888</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178208</t>
+          <t xml:space="preserve">311179271</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-23</t>
+          <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J98">
-        <v>1888</v>
+        <v>281</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Zimmersvej 29</t>
+          <t xml:space="preserve">Birkevangen 4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413132</t>
+          <t xml:space="preserve">7584516</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>281</v>
+        <v>1115</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179271</t>
+          <t xml:space="preserve">311179947</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-05-31</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevangen 4</t>
+          <t xml:space="preserve">Gl. Landevej 62C</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7584516</t>
+          <t xml:space="preserve">3239487</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,11 +7485,11 @@
         </is>
       </c>
       <c r="J100">
-        <v>1115</v>
+        <v>1164</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179947</t>
+          <t xml:space="preserve">311181752</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-31</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 62C</t>
+          <t xml:space="preserve">Idrætsvej 15A</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239487</t>
+          <t xml:space="preserve">3262653</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J101">
-        <v>1164</v>
+        <v>1113</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181752</t>
+          <t xml:space="preserve">311181777</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 15A</t>
+          <t xml:space="preserve">Blokhusvej 47A</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262653</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J102">
-        <v>1113</v>
+        <v>428</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181777</t>
+          <t xml:space="preserve">311190610</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-08</t>
+          <t xml:space="preserve">2026-07-18</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,30 +7691,30 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 47A</t>
+          <t xml:space="preserve">Elmevej 6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3242523</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>428</v>
+        <v>572</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190610</t>
+          <t xml:space="preserve">311207345</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,17 +7724,17 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-18</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmevej 6</t>
+          <t xml:space="preserve">Tjørnevænget 1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242523</t>
+          <t xml:space="preserve">3243120</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>572</v>
+        <v>319</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207345</t>
+          <t xml:space="preserve">311209474</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevænget 1</t>
+          <t xml:space="preserve">Rotfelds Vej 11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243120</t>
+          <t xml:space="preserve">3242161</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>319</v>
+        <v>840</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209474</t>
+          <t xml:space="preserve">311210030</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotfelds Vej 11</t>
+          <t xml:space="preserve">Vester Fælledvej 17</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242161</t>
+          <t xml:space="preserve">3391896</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>840</v>
+        <v>635</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210030</t>
+          <t xml:space="preserve">311210142</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Fælledvej 17</t>
+          <t xml:space="preserve">Svinkløvvej 1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391896</t>
+          <t xml:space="preserve">8826071</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>635</v>
+        <v>575</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210142</t>
+          <t xml:space="preserve">311210311</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinkløvvej 1</t>
+          <t xml:space="preserve">Viaduktvej 28A</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826071</t>
+          <t xml:space="preserve">3257468</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8085,11 +8085,11 @@
         </is>
       </c>
       <c r="J108">
-        <v>575</v>
+        <v>491</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210311</t>
+          <t xml:space="preserve">311210617</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viaduktvej 28A</t>
+          <t xml:space="preserve">Skipper Clements Vej 25</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257468</t>
+          <t xml:space="preserve">3258602</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J109">
-        <v>491</v>
+        <v>747</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210617</t>
+          <t xml:space="preserve">311212446</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skipper Clements Vej 25</t>
+          <t xml:space="preserve">Anlægsvej 1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258602</t>
+          <t xml:space="preserve">3258842</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>747</v>
+        <v>537</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212446</t>
+          <t xml:space="preserve">311212700</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-15</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsvej 1</t>
+          <t xml:space="preserve">Rønnebærvej 8</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258842</t>
+          <t xml:space="preserve">3221223</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>537</v>
+        <v>1422</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212700</t>
+          <t xml:space="preserve">311213714</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-22</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebærvej 8</t>
+          <t xml:space="preserve">Ørebrovej 128</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221223</t>
+          <t xml:space="preserve">9009874</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>1422</v>
+        <v>557</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213714</t>
+          <t xml:space="preserve">311213892</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-22</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8456,15 +8456,15 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>557</v>
+        <v>3128</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213892</t>
+          <t xml:space="preserve">311214103</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørebrovej 128</t>
+          <t xml:space="preserve">Parkvænget 27</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009874</t>
+          <t xml:space="preserve">389901</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J114">
-        <v>3128</v>
+        <v>294</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214103</t>
+          <t xml:space="preserve">311225294</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørtorupvej 2</t>
+          <t xml:space="preserve">Bøge Bakker 7</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387991</t>
+          <t xml:space="preserve">8275117</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J115">
-        <v>422</v>
+        <v>327</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223668</t>
+          <t xml:space="preserve">311226665</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-20</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,30 +8666,30 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvænget 27</t>
+          <t xml:space="preserve">Kordalsvej 13</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">389901</t>
+          <t xml:space="preserve">3235639</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>294</v>
+        <v>396</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225294</t>
+          <t xml:space="preserve">311226663</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøge Bakker 7</t>
+          <t xml:space="preserve">Niels Juels Vej 1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8275117</t>
+          <t xml:space="preserve">7986826</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>327</v>
+        <v>436</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226665</t>
+          <t xml:space="preserve">311229952</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,30 +8816,30 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kordalsvej 13</t>
+          <t xml:space="preserve">Østmarken 2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3235639</t>
+          <t xml:space="preserve">7313030</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J118">
-        <v>396</v>
+        <v>944</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226663</t>
+          <t xml:space="preserve">311236277</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,30 +8891,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Juels Vej 1</t>
+          <t xml:space="preserve">Præstegaardsvej 26C</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7986826</t>
+          <t xml:space="preserve">3227505</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J119">
-        <v>436</v>
+        <v>296</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229952</t>
+          <t xml:space="preserve">311430960</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østmarken 2</t>
+          <t xml:space="preserve">Præstegaardsvej 34</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7313030</t>
+          <t xml:space="preserve">3227457</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>944</v>
+        <v>519</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236277</t>
+          <t xml:space="preserve">311430955</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,40 +9041,40 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 26C</t>
+          <t xml:space="preserve">Stationsvej 20</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227505</t>
+          <t xml:space="preserve">3242155</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>296</v>
+        <v>2615</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430960</t>
+          <t xml:space="preserve">311502859</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-31</t>
+          <t xml:space="preserve">2031-03-12</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 34</t>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227457</t>
+          <t xml:space="preserve">3258795</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,21 +9135,21 @@
         </is>
       </c>
       <c r="J122">
-        <v>519</v>
+        <v>7053</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430955</t>
+          <t xml:space="preserve">311680518</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">Preben Dam ApS</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-31</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,40 +9191,40 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 20</t>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242155</t>
+          <t xml:space="preserve">3258795</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J123">
-        <v>2615</v>
+        <v>1233</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502859</t>
+          <t xml:space="preserve">311680518</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Preben Dam ApS</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-12</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9281,11 +9281,11 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J124">
-        <v>7053</v>
+        <v>413</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -9341,40 +9341,40 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Møllersvej 3</t>
+          <t xml:space="preserve">Jetsmark Kirkevej 5</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258795</t>
+          <t xml:space="preserve">100246402</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>1233</v>
+        <v>8883</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680518</t>
+          <t xml:space="preserve">311687096</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preben Dam ApS</t>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,40 +9416,40 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Møllersvej 3</t>
+          <t xml:space="preserve">Possementmagervej 1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258795</t>
+          <t xml:space="preserve">3231805</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680518</t>
+          <t xml:space="preserve">311788173</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preben Dam ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2034-09-29</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jetsmark Kirkevej 5</t>
+          <t xml:space="preserve">Rønnebærvej 12A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">100246402</t>
+          <t xml:space="preserve">3221313</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,21 +9510,21 @@
         </is>
       </c>
       <c r="J127">
-        <v>8883</v>
+        <v>1423</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311687096</t>
+          <t xml:space="preserve">311853697</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-12</t>
+          <t xml:space="preserve">2035-09-04</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Possementmagervej 1</t>
+          <t xml:space="preserve">Strandvejen 143A</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231805</t>
+          <t xml:space="preserve">8668873</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="J128">
-        <v>410</v>
+        <v>254</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788173</t>
+          <t xml:space="preserve">311873714</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Preben Dam ApS</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-29</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebærvej 12A</t>
+          <t xml:space="preserve">Egevej 8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221313</t>
+          <t xml:space="preserve">389886, 389887, 389888</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>1423</v>
+        <v>2559</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853697</t>
+          <t xml:space="preserve">311888110</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-04</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 143A</t>
+          <t xml:space="preserve">Parkvej 28</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,30 +9726,30 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8668873</t>
+          <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J130">
-        <v>254</v>
+        <v>374</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873708</t>
+          <t xml:space="preserve">311888109</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevej 8</t>
+          <t xml:space="preserve">Sygehusvej 14</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">389886, 389887, 389888</t>
+          <t xml:space="preserve">3243191</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,21 +9810,21 @@
         </is>
       </c>
       <c r="J131">
-        <v>2559</v>
+        <v>3319</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888110</t>
+          <t xml:space="preserve">311898289</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 28</t>
+          <t xml:space="preserve">Sygehusvej 6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,30 +9876,30 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
+          <t xml:space="preserve">3243191</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J132">
-        <v>374</v>
+        <v>1558</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888109</t>
+          <t xml:space="preserve">311898289</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 14</t>
+          <t xml:space="preserve">Vestergade 9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243191</t>
+          <t xml:space="preserve">389878</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,21 +9960,21 @@
         </is>
       </c>
       <c r="J133">
-        <v>3319</v>
+        <v>1788</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898289</t>
+          <t xml:space="preserve">311901807</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-01</t>
+          <t xml:space="preserve">2036-05-18</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,40 +10016,40 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 6</t>
+          <t xml:space="preserve">Kattedamsvej 32B</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243191</t>
+          <t xml:space="preserve">3258634</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J134">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898289</t>
+          <t xml:space="preserve">311902872</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-01</t>
+          <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,30 +10091,30 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 9</t>
+          <t xml:space="preserve">Nørtorupvej 2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">389878</t>
+          <t xml:space="preserve">3387991</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J135">
-        <v>1788</v>
+        <v>422</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901807</t>
+          <t xml:space="preserve">311926435</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-18</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,40 +10166,40 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattedamsvej 32B</t>
+          <t xml:space="preserve">Hjortdalvej 148</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258634</t>
+          <t xml:space="preserve">3387991</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>1552</v>
+        <v>1013</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311902872</t>
+          <t xml:space="preserve">311927258</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artelia A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-21</t>
+          <t xml:space="preserve">2036-09-22</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">

--- a/public/exports/29189439.xlsx
+++ b/public/exports/29189439.xlsx
@@ -7729,12 +7729,12 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873714</t>
+          <t xml:space="preserve">311873708</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preben Dam ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M128" t="inlineStr">
